--- a/data/三航杯赛程.xlsx
+++ b/data/三航杯赛程.xlsx
@@ -511,6 +511,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -721,11 +722,15 @@
           <t>航空</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
+      <c r="F9" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已结束</t>
         </is>
       </c>
     </row>

--- a/data/三航杯赛程.xlsx
+++ b/data/三航杯赛程.xlsx
@@ -758,11 +758,15 @@
           <t>航天</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
+      <c r="F10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已结束</t>
         </is>
       </c>
     </row>

--- a/data/三航杯赛程.xlsx
+++ b/data/三航杯赛程.xlsx
@@ -794,11 +794,15 @@
           <t>力载</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已结束</t>
         </is>
       </c>
     </row>

--- a/data/三航杯赛程.xlsx
+++ b/data/三航杯赛程.xlsx
@@ -511,7 +511,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -830,11 +829,15 @@
           <t>数统</t>
         </is>
       </c>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
+      <c r="F12" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>已结束</t>
         </is>
       </c>
     </row>
